--- a/YoY_gross_tickets.xlsx
+++ b/YoY_gross_tickets.xlsx
@@ -508,14 +508,14 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8000149.1</v>
+        <v>8000164.5</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>4755938.2</v>
+        <v>5568199.1</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-30.4%</t>
         </is>
       </c>
     </row>
@@ -526,14 +526,14 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>6121355.3</v>
+        <v>6120744.2</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3756637.5</v>
+        <v>4966288.1</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-18.9%</t>
         </is>
       </c>
     </row>
@@ -544,14 +544,14 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2772612.166666667</v>
+        <v>2772943.466666667</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>9110801.5</v>
+        <v>10761052</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+228.6%</t>
+          <t>+288.1%</t>
         </is>
       </c>
     </row>
@@ -562,14 +562,14 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>28487.2</v>
+        <v>28514.1</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>44750.8</v>
+        <v>44828.1</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+57.1%</t>
+          <t>+57.2%</t>
         </is>
       </c>
     </row>
@@ -580,14 +580,14 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>904750.4</v>
+        <v>905268</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>741611.3</v>
+        <v>875831.7</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
     </row>
@@ -598,14 +598,14 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>13449602.25</v>
+        <v>13449246.35</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>10839972</v>
+        <v>12456133.6</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
@@ -616,14 +616,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>31276956.41666666</v>
+        <v>31276880.61666667</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>29249711.3</v>
+        <v>34672332.6</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>+10.9%</t>
         </is>
       </c>
     </row>
@@ -664,14 +664,14 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>8011597.4</v>
+        <v>8011612.8</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4974078</v>
+        <v>5786387.5</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-27.8%</t>
         </is>
       </c>
     </row>
@@ -682,14 +682,14 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>6121355.3</v>
+        <v>6120744.2</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3859113.2</v>
+        <v>5068365.3</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-17.2%</t>
         </is>
       </c>
     </row>
@@ -700,14 +700,14 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>3375269.5</v>
+        <v>3375600.8</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9155226.699999999</v>
+        <v>10805613</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+171.2%</t>
+          <t>+220.1%</t>
         </is>
       </c>
     </row>
@@ -718,14 +718,14 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>28716.6</v>
+        <v>28743.5</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>44750.8</v>
+        <v>44828.1</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+55.8%</t>
+          <t>+56.0%</t>
         </is>
       </c>
     </row>
@@ -736,14 +736,14 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>926892.4</v>
+        <v>927407</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>763874.3</v>
+        <v>898349.5</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
@@ -754,14 +754,14 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>13732158</v>
+        <v>13731802.1</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>11101720.9</v>
+        <v>12717851.7</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
@@ -772,14 +772,14 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>32195989.2</v>
+        <v>32195910.4</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>29898763.9</v>
+        <v>35321395.1</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>+9.7%</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -847,14 +847,14 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>991068082.0599999</v>
+        <v>991122496.17</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>532700654.5383334</v>
+        <v>629565340.1683333</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-46.2%</t>
+          <t>-36.5%</t>
         </is>
       </c>
     </row>
@@ -865,14 +865,14 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>373971388.85</v>
+        <v>374214336.47</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>221197305.51</v>
+        <v>309500170.48</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-17.3%</t>
         </is>
       </c>
     </row>
@@ -883,14 +883,14 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>363914356.0266666</v>
+        <v>364564763.2466667</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1408873041.78</v>
+        <v>1674711723.16</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+287.1%</t>
+          <t>+359.4%</t>
         </is>
       </c>
     </row>
@@ -901,14 +901,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1035534.51</v>
+        <v>1037751.52</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1590772.24</v>
+        <v>1593340.76</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+53.6%</t>
+          <t>+53.5%</t>
         </is>
       </c>
     </row>
@@ -919,14 +919,14 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>72435905.77</v>
+        <v>72489677.12</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>63174719.67</v>
+        <v>70946680.33</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-2.1%</t>
         </is>
       </c>
     </row>
@@ -937,14 +937,14 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1843628069.8375</v>
+        <v>1843850715.0475</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1532480483.035</v>
+        <v>1792073428.105</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
     </row>
@@ -955,14 +955,14 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3646053337.054167</v>
+        <v>3647279739.574166</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3760016976.773334</v>
+        <v>4478390683.003334</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+22.8%</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1003,14 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>992145098.395</v>
+        <v>992199512.505</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>550238421.75</v>
+        <v>647139366.66</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-34.8%</t>
         </is>
       </c>
     </row>
@@ -1021,14 +1021,14 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>373971388.85</v>
+        <v>374214336.47</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>226144707.86</v>
+        <v>314433843.91</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-16.0%</t>
         </is>
       </c>
     </row>
@@ -1039,14 +1039,14 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>438031580.15</v>
+        <v>438681987.37</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1414654659.26</v>
+        <v>1680627060.58</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+223.0%</t>
+          <t>+283.1%</t>
         </is>
       </c>
     </row>
@@ -1057,14 +1057,14 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1041321.96</v>
+        <v>1043538.97</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1590772.24</v>
+        <v>1593340.76</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+52.8%</t>
+          <t>+52.7%</t>
         </is>
       </c>
     </row>
@@ -1075,14 +1075,14 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>75597091.77</v>
+        <v>75650521.37</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>64565888.49</v>
+        <v>72338597.51000001</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
     </row>
@@ -1093,14 +1093,14 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1877179566.575</v>
+        <v>1877402211.785</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1557853341.87</v>
+        <v>1817460769.21</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-3.2%</t>
         </is>
       </c>
     </row>
@@ -1111,14 +1111,14 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>3757966047.7</v>
+        <v>3759192108.47</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>3815047791.469999</v>
+        <v>4533592978.63</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>+20.6%</t>
         </is>
       </c>
     </row>
@@ -1189,11 +1189,11 @@
         <v>6740935</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3453397.2</v>
+        <v>4455053.2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-33.9%</t>
         </is>
       </c>
     </row>
@@ -1207,11 +1207,11 @@
         <v>5107195.5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2555282.5</v>
+        <v>4042657.5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -1225,11 +1225,11 @@
         <v>1850380.166666667</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>8158819</v>
+        <v>10187056</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+340.9%</t>
+          <t>+450.5%</t>
         </is>
       </c>
     </row>
@@ -1261,11 +1261,11 @@
         <v>672319</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>426931.5</v>
+        <v>545215.5</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-18.9%</t>
         </is>
       </c>
     </row>
@@ -1279,11 +1279,11 @@
         <v>11666577.75</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>8639063.5</v>
+        <v>10526739.5</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-9.8%</t>
         </is>
       </c>
     </row>
@@ -1297,11 +1297,11 @@
         <v>26050002.41666666</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>23257863.7</v>
+        <v>29781091.7</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>+14.3%</t>
         </is>
       </c>
     </row>
@@ -1345,11 +1345,11 @@
         <v>6751472.5</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3629698.5</v>
+        <v>4631354.5</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>-46.2%</t>
+          <t>-31.4%</t>
         </is>
       </c>
     </row>
@@ -1363,11 +1363,11 @@
         <v>5107195.5</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2555282.5</v>
+        <v>4042657.5</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -1381,11 +1381,11 @@
         <v>2433677.5</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>8158819</v>
+        <v>10187056</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+235.2%</t>
+          <t>+318.6%</t>
         </is>
       </c>
     </row>
@@ -1417,11 +1417,11 @@
         <v>693658</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>437291.5</v>
+        <v>555575.5</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-19.9%</t>
         </is>
       </c>
     </row>
@@ -1435,11 +1435,11 @@
         <v>11949133.5</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>8729968.5</v>
+        <v>10617644.5</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-11.1%</t>
         </is>
       </c>
     </row>
@@ -1453,11 +1453,11 @@
         <v>26947732</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>23535430</v>
+        <v>30058658</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>+11.5%</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1528,11 +1528,11 @@
         <v>863948447.23</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>412205852.5083333</v>
+        <v>524586228.1083333</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-52.3%</t>
+          <t>-39.3%</t>
         </is>
       </c>
     </row>
@@ -1546,11 +1546,11 @@
         <v>318914244.23</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>161761586.15</v>
+        <v>263203806.85</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
@@ -1564,11 +1564,11 @@
         <v>239033068.7566667</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1281284978.27</v>
+        <v>1595705881.24</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+436.0%</t>
+          <t>+567.6%</t>
         </is>
       </c>
     </row>
@@ -1600,11 +1600,11 @@
         <v>58322659.93</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>39739153.68</v>
+        <v>46190256.49</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -1618,11 +1618,11 @@
         <v>1618202230.5875</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1276481560.065</v>
+        <v>1566341239.615</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
     </row>
@@ -1636,11 +1636,11 @@
         <v>3099012480.294167</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3172395261.383333</v>
+        <v>3996949543.013333</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+29.0%</t>
         </is>
       </c>
     </row>
@@ -1684,11 +1684,11 @@
         <v>864955216.655</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>426564901.04</v>
+        <v>538945276.64</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-37.7%</t>
         </is>
       </c>
     </row>
@@ -1702,11 +1702,11 @@
         <v>318914244.23</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>161761586.15</v>
+        <v>263203806.85</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
     </row>
@@ -1720,11 +1720,11 @@
         <v>310249678.88</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1281284978.27</v>
+        <v>1595705881.24</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+313.0%</t>
+          <t>+414.3%</t>
         </is>
       </c>
     </row>
@@ -1756,11 +1756,11 @@
         <v>61440496.38</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>40460578.68</v>
+        <v>46911681.49</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-23.6%</t>
         </is>
       </c>
     </row>
@@ -1774,11 +1774,11 @@
         <v>1651753727.325</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1283949142.23</v>
+        <v>1573808821.78</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-4.7%</t>
         </is>
       </c>
     </row>
@@ -1792,11 +1792,11 @@
         <v>3207905193.03</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>3194943317.08</v>
+        <v>4019497598.71</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>+25.3%</t>
         </is>
       </c>
     </row>
@@ -1864,14 +1864,14 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>806807.7</v>
+        <v>806840.3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>789312.4666666667</v>
+        <v>868051.8666666667</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>+7.6%</t>
         </is>
       </c>
     </row>
@@ -1882,14 +1882,14 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5209042.4</v>
+        <v>5208115.7</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3420204.3</v>
+        <v>4402360.6</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-15.5%</t>
         </is>
       </c>
     </row>
@@ -1900,14 +1900,14 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>161356.4</v>
+        <v>161382.4</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1394451.6</v>
+        <v>1776605</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+764.2%</t>
+          <t>+1000.9%</t>
         </is>
       </c>
     </row>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>28487.2</v>
+        <v>28514.1</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>43968.1</v>
+        <v>43995</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -1936,14 +1936,14 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>356027.3</v>
+        <v>356406.7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>407736.9</v>
+        <v>463594.9</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>+14.5%</t>
+          <t>+30.1%</t>
         </is>
       </c>
     </row>
@@ -1972,14 +1972,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6646069.000000001</v>
+        <v>6645607.2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>6148484.966666667</v>
+        <v>7647418.966666667</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>+15.1%</t>
         </is>
       </c>
     </row>
@@ -2020,14 +2020,14 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>806807.7</v>
+        <v>806840.3</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>885410.2333333333</v>
+        <v>964158.5333333333</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>+19.5%</t>
         </is>
       </c>
     </row>
@@ -2038,14 +2038,14 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>5209042.4</v>
+        <v>5208115.7</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3513177</v>
+        <v>4494934.8</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-13.7%</t>
         </is>
       </c>
     </row>
@@ -2056,14 +2056,14 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>161356.4</v>
+        <v>161382.4</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1394451.6</v>
+        <v>1776605</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+764.2%</t>
+          <t>+1000.9%</t>
         </is>
       </c>
     </row>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>28716.6</v>
+        <v>28743.5</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>43968.1</v>
+        <v>43995</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -2092,14 +2092,14 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>356830.3</v>
+        <v>357206.7</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>414199.4</v>
+        <v>470284</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>+16.1%</t>
+          <t>+31.7%</t>
         </is>
       </c>
     </row>
@@ -2128,14 +2128,14 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>6647101.4</v>
+        <v>6646636.600000001</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>6344017.933333334</v>
+        <v>7842788.933333333</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>+18.0%</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2203,14 +2203,14 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>89109653.73</v>
+        <v>89111723.73</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>85069635.75666666</v>
+        <v>92152844.77666667</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>+3.4%</t>
         </is>
       </c>
     </row>
@@ -2221,14 +2221,14 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>313857402.78</v>
+        <v>314072455.12</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>199310225.2</v>
+        <v>270966479.45</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-13.7%</t>
         </is>
       </c>
     </row>
@@ -2239,14 +2239,14 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>14876735.8</v>
+        <v>14884700.2</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>169476326.26</v>
+        <v>218023221.86</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+1039.2%</t>
+          <t>+1364.7%</t>
         </is>
       </c>
     </row>
@@ -2257,14 +2257,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1035534.51</v>
+        <v>1037751.52</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1555872.89</v>
+        <v>1557641.01</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+50.2%</t>
+          <t>+50.1%</t>
         </is>
       </c>
     </row>
@@ -2275,14 +2275,14 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>27545663.8</v>
+        <v>27597348.72</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>33345855.58</v>
+        <v>36138826.5</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>+21.1%</t>
+          <t>+31.0%</t>
         </is>
       </c>
     </row>
@@ -2311,14 +2311,14 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>458337562.16</v>
+        <v>458616550.83</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>508562447.9816666</v>
+        <v>638643545.8916667</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+11.0%</t>
+          <t>+39.3%</t>
         </is>
       </c>
     </row>
@@ -2359,14 +2359,14 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>89109653.73</v>
+        <v>89111723.73</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>92512931.55333334</v>
+        <v>99596768.97333333</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+11.8%</t>
         </is>
       </c>
     </row>
@@ -2377,14 +2377,14 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>313857402.78</v>
+        <v>314072455.12</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>203677838.18</v>
+        <v>275320363.51</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-12.3%</t>
         </is>
       </c>
     </row>
@@ -2395,14 +2395,14 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>14876735.8</v>
+        <v>14884700.2</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>169476326.26</v>
+        <v>218023221.86</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+1039.2%</t>
+          <t>+1364.7%</t>
         </is>
       </c>
     </row>
@@ -2413,14 +2413,14 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1041321.96</v>
+        <v>1043538.97</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1555872.89</v>
+        <v>1557641.01</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+49.4%</t>
+          <t>+49.3%</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>27589013.35</v>
+        <v>27640356.52</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>33694988.95</v>
+        <v>36487959.87</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>+22.1%</t>
+          <t>+32.0%</t>
         </is>
       </c>
     </row>
@@ -2467,14 +2467,14 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>458386699.16</v>
+        <v>458665346.08</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>520722490.1283333</v>
+        <v>650790487.5183333</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>+13.6%</t>
+          <t>+41.9%</t>
         </is>
       </c>
     </row>
